--- a/review/abilities/workbooks/21_Class_Blade.xlsx
+++ b/review/abilities/workbooks/21_Class_Blade.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -197,7 +197,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -234,19 +234,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -869,7 +856,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Cut and Turn; Pressure Point; Measured Guard</t>
+          <t>Reckless Charge; Cleave; Measured Guard</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -889,7 +876,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Sweeping Entry; Return Stroke; Fell the Balance</t>
+          <t>Sweeping Entry; Return Stroke; Not So Fast</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -1039,8 +1026,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -1191,50 +1178,50 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="79" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Cut and Turn</t>
+          <t>Cleave</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-blade-cut-and-turn</t>
+          <t>signature-blade-pressure-point</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self, after your Main Action melee attack resolves.</t>
+          <t>All creatures adjacent to you, including allies. You must be wielding a melee weapon.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 1 square without provoking. On a Standard or Strong attack, you may move up to 2 squares instead. Use a legal route and free endpoint; this grants no additional attack.</t>
+          <t>Make one Brawn roll. On a Weak result, deal 1 damage to each creature adjacent to you. On a Standard result, deal 1 damage and push each creature 1 square directly away from you. On a Strong result, deal 1 damage and push each creature 2 squares directly away from you. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 1 square without provoking. On a Standard or Strong attack, you may move up to 2 squares instead. Use a legal route and free endpoint; this grants no additional attack.</t>
+          <t>Make one Brawn roll. On a Weak result, deal 1 damage to each creature adjacent to you. On a Standard result, deal 1 damage and push each creature 1 square directly away from you. On a Strong result, deal 1 damage and push each creature 2 squares directly away from you. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Free 1-2 square move after a melee attack; core mobility and the simplest expression of the Blade's tempo.</t>
+          <t>Cleave: Main Action Brawn attack against every adjacent creature, including allies. Weak deals 1 damage, Standard adds push 1, Strong adds push 2. Strong area control with friendly fire.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>No change needed. The text is clear that the move is after the attack resolves and grants no extra attack.</t>
+          <t>Approved: Main Action, Brawn, all adjacent creatures including allies; Weak 1 damage, Standard 1 damage plus push 1, Strong 1 damage plus push 2. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1268,7 +1255,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1278,22 +1265,22 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Gain 1 Boon to the defense. After the attack resolves, you may move up to 2 squares without provoking, whatever the defense result. This does not prevent the attack’s damage or conditions; you must still be able to move.</t>
+          <t>Gain 1 Boon to the defense. After the attack resolves, if the defense was Strong and the attacker is within your reach, make a Basic Melee attack against that attacker. This counterattack is part of the Reaction and does not use your Main Action.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Gain 1 Boon to the defense. After the attack resolves, you may move up to 2 squares without provoking, whatever the defense result. This does not prevent the attack’s damage or conditions; you must still be able to move.</t>
+          <t>Gain 1 Boon to the defense. After the attack resolves, if the defense was Strong and the attacker is within your reach, make a Basic Melee attack against that attacker. This counterattack is part of the Reaction and does not use your Main Action.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Reaction for 1 Boon to defense plus a 2-square move whatever the result; excellent skirmisher action economy.</t>
+          <t>Reaction for 1 Boon to defense, plus a Basic Melee counterattack on a Strong defense. Strong defensive punishment and a clear reason to guard.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Strong but appropriate for level 1. Clarify that the movement is optional and still requires a legal route.</t>
+          <t>Approved: 1 Boon to defense; on Strong, Basic Melee against the attacker if within reach; the counterattack is part of the Reaction and does not use the Main Action.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1309,50 +1296,50 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="41.5" customHeight="1">
+    <row r="7" ht="91.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Pressure Point</t>
+          <t>Reckless Charge</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-blade-pressure-point</t>
+          <t>signature-blade-cut-and-turn</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One target of your Main Action melee attack.</t>
+          <t>Self; move up to 2 squares toward an enemy, then make a Basic Melee attack against a creature within reach.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>After a Standard result, apply Slowed 1 to one target. After Strong, apply Slowed 2 instead. The attack otherwise resolves normally.</t>
+          <t>Move up to 2 squares toward an enemy you can see. Then make a Basic Melee attack against a creature within reach. This attack is part of the Maneuver, so your Main Action remains available. On a Weak result, deal 1 extra damage; on a Standard result, deal 2 extra damage; on a Strong result, deal 3 extra damage.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>After a Standard result, apply Slowed 1 to one target. After Strong, apply Slowed 2 instead. The attack otherwise resolves normally.</t>
+          <t>Move up to 2 squares toward an enemy you can see. Then make a Basic Melee attack against a creature within reach. This attack is part of the Maneuver, so your Main Action remains available. On a Weak result, deal 1 extra damage; on a Standard result, deal 2 extra damage; on a Strong result, deal 3 extra damage. Take 1 Bane on defense rolls until the beginning of your next turn. This movement follows normal opportunity attack rules.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Slowed 1/2 rider on a Standard/Strong melee hit; control without spending another action.</t>
+          <t>Reckless Charge: Maneuver move up to 2 squares and make a Basic Melee attack as part of the Maneuver, with 1, 2 or 3 extra damage by result. Your Main Action remains available, at the cost of 1 Bane on defense until your next turn.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether Slowed stacks with other Slowed contributions and whether it applies before the target's next turn. Add a short condition reminder.</t>
+          <t>Approved: Maneuver, move 2 toward an enemy, Basic Melee as part of the Maneuver, +1/2/3 damage by result, 1 Bane on defense until next turn, normal opportunity attacks.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1385,15 +1372,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1520,7 +1504,7 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Fell the Balance</t>
+          <t>Not So Fast</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1530,37 +1514,37 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>One target of your Standard or Strong Main Action melee attack.</t>
+          <t>One enemy that voluntarily enters a square you threaten from outside your reach.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>After the attack resolves, you may knock that target prone. This does not require a push rider or replace another effect. It adds no damage and cannot turn Prone into a numbered condition.</t>
+          <t>Make a Basic Melee attack against the triggering enemy. After the attack resolves, the enemy’s movement ends, and it cannot move again until the start of its next turn.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>After the attack resolves, you may knock that target prone. This does not require a push rider or replace another effect. It adds no damage and cannot turn Prone into a numbered condition.</t>
+          <t>Make a Basic Melee attack against the triggering enemy. After the attack resolves, the enemy’s movement ends, and it cannot move again until the start of its next turn.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Knocks a target prone on a Standard/Strong melee hit; strong control with no extra roll.</t>
+          <t>Not So Fast: Reaction when an enemy voluntarily enters reach; make a Basic Melee attack and halt its movement until its next turn. Strong zone control.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify that Prone is applied after damage and before the target acts, and whether it can affect a target that is already prone (wasted).</t>
+          <t>Approved: Reaction, Brawn, voluntary entry from outside reach, Basic Melee attack, movement ends and cannot move until the start of its next turn, once per round.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1594,7 +1578,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1604,32 +1588,32 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Make one free Basic Melee attack against it, rolling Brawn and using Basic Melee’s outcomes. You need a melee weapon and must still be able to attack. A triggering free attack cannot trigger this free attack. No further free attacks arise from your return stroke.</t>
+          <t>Make one free Basic Melee attack against the attacker after a Standard or Strong defense.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Make one free Basic Melee attack against it, rolling Brawn and using Basic Melee’s outcomes. You need a melee weapon and must still be able to attack. A triggering free attack cannot trigger this free attack. No further free attacks arise from your return stroke.</t>
+          <t>Make one free Basic Melee attack against it, rolling Brawn and using Basic Melee’s outcomes. This requires a melee weapon and the ability to attack. This is a single free attack.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Free Basic Melee after a Standard/Strong defense; a strong counterattack that rewards defensive rolls.</t>
+          <t>Reaction for one free Basic Melee after a Standard or Strong defense. Strong counterattack and a direct competitor to the other Blade Reactions.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>This is a free attack every round against a melee attacker. Playtest; keep the no-chain clause prominent and clarify that it uses the Blade's own weapon.</t>
+          <t>Approved: positive wording; one free Basic Melee attack, requires a melee weapon and the ability to attack, single free attack.</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Free attack</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1643,52 +1627,52 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-blade-sweeping-entry</t>
+          <t>Twitch Reflexes</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Self; a visible enemy you can approach by a legal route.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Move up to 3 squares toward that enemy without provoking. Your next Main Action melee attack this turn may push one of its targets 1 square directly away after resolution, on any result.</t>
+          <t>You can take one additional Reaction each round.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Move up to 3 squares toward that enemy without provoking. Your next Main Action melee attack this turn may push one of its targets 1 square directly away after resolution, on any result.</t>
+          <t>You can take one additional Reaction each round.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Move 3 toward an enemy and set up a 1-square push on the next melee attack; good approach and setup.</t>
+          <t>Twitch Reflexes: one additional Reaction each round. Simple, powerful and a direct force multiplier for the Blade's Reaction options.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify that the push benefit is not lost on a miss (text says on any result) and that the movement still provokes normally.</t>
+          <t>Approved: passive; one additional Reaction each round.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -1711,15 +1695,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1743,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1914,52 +1895,52 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-blade-perfect-placement</t>
+          <t>Get Out of Here</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One target of your Standard or Strong Main Action melee attack, then self.</t>
+          <t>One adjacent creature your size or smaller. You must have a free hand.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>After resolving the attack, push the target up to 2 squares directly away from you. Then you may move up to 2 squares without provoking. Resolve both in order along legal routes; normal collision rules apply to the push.</t>
+          <t>Throw an adjacent creature 3/5/7 squares in any direction; Standard adds Dazed 1, Strong adds Dazed 2. It lands prone.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>After resolving the attack, push the target up to 2 squares directly away from you. Then you may move up to 2 squares without provoking. Resolve both in order along legal routes; normal collision rules apply to the push.</t>
+          <t>Make a Brawn roll against the target. On a Weak result, throw it 3 squares. On a Standard result, throw it 5 squares and apply Dazed 1. On a Strong result, throw it 7 squares and apply Dazed 2. Choose the direction. The target lands prone. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Push 2 then move 2 after a Standard/Strong attack; simple battlefield shaping.</t>
+          <t>Get Out of Here: Main Action Brawn throw against an adjacent creature your size or smaller. Throw 3 squares on Weak, 5 plus Dazed 1 on Standard, 7 plus Dazed 2 on Strong; any direction, lands prone, collisions normal.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Modest for Master. Consider push 3 or letting an ally move instead; at minimum, make sure it feels distinct from Cut and Turn.</t>
+          <t>Approved: Main Action, Brawn, adjacent creature your size or smaller, free hand, 3/5/7 squares, Dazed 1/2, any direction, prone, collisions normal.</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Master feel</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1978,51 +1959,102 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>A visible enemy within 2 squares when it begins voluntary movement.</t>
+          <t>Up to three distinct adjacent enemies.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>After it finishes moving, move up to your Speed toward it without provoking. If you end adjacent, you may make one free Basic Melee attack against it using Brawn. Choose a legal route and endpoint; this does not stop or rewind its movement.</t>
+          <t>One Agility roll against up to three adjacent enemies. Weak 4 damage; Standard 4 damage and move 1; Strong 6 damage and move 2.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>After it finishes moving, move up to your Speed toward it without provoking. If you end adjacent, you may make one free Basic Melee attack against it using Brawn. Choose a legal route and endpoint; this does not stop or rewind its movement. If that movement was granted by a free attack, it cannot trigger this card’s free attack. No attack chains.</t>
+          <t>Choose up to three distinct adjacent enemies and roll Agility once using the least favorable net Boons/Banes among them.
+- Weak: Deal 4 physical damage to each.
+- Standard: Deal 4 physical damage to each, then you may move up to 1 square without provoking.
+- Strong: Deal 6 physical damage to each, then you may move up to 2 squares without provoking.
+This is one signature attack against all chosen targets. Choose all targets before rolling.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Reaction chase at full Speed plus a free attack when an enemy moves within 2. Potentially very strong and very thematic.</t>
+          <t>Master AoE: one Agility roll, 4/4/6 damage to up to three adjacent enemies, plus movement. Good Master-scale attack.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Consider once per round or a shorter chase. Playtest whether it triggers too often in open combat; the voluntary-movement clause is good.</t>
+          <t>Approved: positive wording. Choose all targets before rolling; one Agility roll applies to all, with optional movement after damage.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Free attack</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Reaction</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A visible enemy within 2 squares when it begins voluntary movement.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Chase up to your Speed after the enemy moves; if adjacent, make a free Basic Melee with 1 Boon and apply Slowed 1, 2 or 3 by result.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>After it finishes moving, move up to your Speed toward it without provoking. If you end adjacent, make one free Basic Melee attack against it using Brawn with 1 Boon. On a Weak result, apply Slowed 1. On a Standard result, apply Slowed 2. On a Strong result, apply Slowed 3. Slowed uses normal decay.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Reaction chase at full Speed plus a free Basic Melee with 1 Boon, then Slowed 1, 2 or 3 by result. Strong Master pursuit and a real escape punishment.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Approved: Reaction, voluntary movement within 2, full Speed chase without provoking, free Basic Melee with 1 Boon if adjacent, Slowed 1/2/3 by result, normal decay.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -2041,15 +2073,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2173,7 +2202,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="79" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2181,42 +2210,42 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Cut and Turn</t>
+          <t>Cleave</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>signature-blade-cut-and-turn</t>
+          <t>signature-blade-pressure-point</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Self, after your Main Action melee attack resolves.</t>
+          <t>All creatures adjacent to you, including allies. You must be wielding a melee weapon.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 1 square without provoking. On a Standard or Strong attack, you may move up to 2 squares instead. Use a legal route and free endpoint; this grants no additional attack.</t>
+          <t>Make one Brawn roll. On a Weak result, deal 1 damage to each creature adjacent to you. On a Standard result, deal 1 damage and push each creature 1 square directly away from you. On a Strong result, deal 1 damage and push each creature 2 squares directly away from you. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Free 1-2 square move after a melee attack; core mobility and the simplest expression of the Blade's tempo.</t>
+          <t>Cleave: Main Action Brawn attack against every adjacent creature, including allies. Weak deals 1 damage, Standard adds push 1, Strong adds push 2. Strong area control with friendly fire.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>No change needed. The text is clear that the move is after the attack resolves and grants no extra attack.</t>
+          <t>Approved: Main Action, Brawn, all adjacent creatures including allies; Weak 1 damage, Standard 1 damage plus push 1, Strong 1 damage plus push 2. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -2255,7 +2284,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2265,17 +2294,17 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Gain 1 Boon to the defense. After the attack resolves, you may move up to 2 squares without provoking, whatever the defense result. This does not prevent the attack’s damage or conditions; you must still be able to move.</t>
+          <t>Gain 1 Boon to the defense. After the attack resolves, if the defense was Strong and the attacker is within your reach, make a Basic Melee attack against that attacker. This counterattack is part of the Reaction and does not use your Main Action.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Reaction for 1 Boon to defense plus a 2-square move whatever the result; excellent skirmisher action economy.</t>
+          <t>Reaction for 1 Boon to defense, plus a Basic Melee counterattack on a Strong defense. Strong defensive punishment and a clear reason to guard.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Strong but appropriate for level 1. Clarify that the movement is optional and still requires a legal route.</t>
+          <t>Approved: 1 Boon to defense; on Strong, Basic Melee against the attacker if within reach; the counterattack is part of the Reaction and does not use the Main Action.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -2291,7 +2320,7 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="41.5" customHeight="1">
+    <row r="7" ht="91.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2299,42 +2328,42 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Pressure Point</t>
+          <t>Reckless Charge</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>signature-blade-pressure-point</t>
+          <t>signature-blade-cut-and-turn</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>One target of your Main Action melee attack.</t>
+          <t>Self; move up to 2 squares toward an enemy, then make a Basic Melee attack against a creature within reach.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>After a Standard result, apply Slowed 1 to one target. After Strong, apply Slowed 2 instead. The attack otherwise resolves normally.</t>
+          <t>Move up to 2 squares toward an enemy you can see. Then make a Basic Melee attack against a creature within reach. This attack is part of the Maneuver, so your Main Action remains available. On a Weak result, deal 1 extra damage; on a Standard result, deal 2 extra damage; on a Strong result, deal 3 extra damage.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Slowed 1/2 rider on a Standard/Strong melee hit; control without spending another action.</t>
+          <t>Reckless Charge: Maneuver move up to 2 squares and make a Basic Melee attack as part of the Maneuver, with 1, 2 or 3 extra damage by result. Your Main Action remains available, at the cost of 1 Bane on defense until your next turn.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether Slowed stacks with other Slowed contributions and whether it applies before the target's next turn. Add a short condition reminder.</t>
+          <t>Approved: Maneuver, move 2 toward an enemy, Basic Melee as part of the Maneuver, +1/2/3 damage by result, 1 Bane on defense until next turn, normal opportunity attacks.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2358,7 +2387,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Fell the Balance</t>
+          <t>Not So Fast</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -2368,32 +2397,32 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>One target of your Standard or Strong Main Action melee attack.</t>
+          <t>One enemy that voluntarily enters a square you threaten from outside your reach.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>After the attack resolves, you may knock that target prone. This does not require a push rider or replace another effect. It adds no damage and cannot turn Prone into a numbered condition.</t>
+          <t>Make a Basic Melee attack against the triggering enemy. After the attack resolves, the enemy’s movement ends, and it cannot move again until the start of its next turn.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Knocks a target prone on a Standard/Strong melee hit; strong control with no extra roll.</t>
+          <t>Not So Fast: Reaction when an enemy voluntarily enters reach; make a Basic Melee attack and halt its movement until its next turn. Strong zone control.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Clarify that Prone is applied after damage and before the target acts, and whether it can affect a target that is already prone (wasted).</t>
+          <t>Approved: Reaction, Brawn, voluntary entry from outside reach, Basic Melee attack, movement ends and cannot move until the start of its next turn, once per round.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -2432,7 +2461,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2442,17 +2471,17 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Make one free Basic Melee attack against it, rolling Brawn and using Basic Melee’s outcomes. You need a melee weapon and must still be able to attack. A triggering free attack cannot trigger this free attack. No further free attacks arise from your return stroke.</t>
+          <t>Make one free Basic Melee attack against the attacker after a Standard or Strong defense.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Free Basic Melee after a Standard/Strong defense; a strong counterattack that rewards defensive rolls.</t>
+          <t>Reaction for one free Basic Melee after a Standard or Strong defense. Strong counterattack and a direct competitor to the other Blade Reactions.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>This is a free attack every round against a melee attacker. Playtest; keep the no-chain clause prominent and clarify that it uses the Blade's own weapon.</t>
+          <t>Approved: positive wording; one free Basic Melee attack, requires a melee weapon and the ability to attack, single free attack.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -2476,7 +2505,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Sweeping Entry</t>
+          <t>Twitch Reflexes</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -2486,32 +2515,32 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Self; a visible enemy you can approach by a legal route.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Move up to 3 squares toward that enemy without provoking. Your next Main Action melee attack this turn may push one of its targets 1 square directly away after resolution, on any result.</t>
+          <t>You can take one additional Reaction each round.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Move 3 toward an enemy and set up a 1-square push on the next melee attack; good approach and setup.</t>
+          <t>Twitch Reflexes: one additional Reaction each round. Simple, powerful and a direct force multiplier for the Blade's Reaction options.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Clarify that the push benefit is not lost on a miss (text says on any result) and that the movement still provokes normally.</t>
+          <t>Approved: passive; one additional Reaction each round.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -2560,7 +2589,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Choose the targets and roll Agility once using the least favorable net Boons/Banes among them.</t>
+          <t>One Agility roll against up to three adjacent enemies. Weak 4 damage; Standard 4 damage and move 1; Strong 6 damage and move 2.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2570,7 +2599,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Clarify that 'least favorable' applies across all targets and that movement happens after all damage. Good as written otherwise.</t>
+          <t>Approved: positive wording. Choose all targets before rolling; one Agility roll applies to all, with optional movement after damage.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -2594,7 +2623,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Perfect Placement</t>
+          <t>Get Out of Here</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2604,32 +2633,32 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>One target of your Standard or Strong Main Action melee attack, then self.</t>
+          <t>One adjacent creature your size or smaller. You must have a free hand.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>After resolving the attack, push the target up to 2 squares directly away from you. Then you may move up to 2 squares without provoking. Resolve both in order along legal routes; normal collision rules apply to the push.</t>
+          <t>Throw an adjacent creature 3/5/7 squares in any direction; Standard adds Dazed 1, Strong adds Dazed 2. It lands prone.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Push 2 then move 2 after a Standard/Strong attack; simple battlefield shaping.</t>
+          <t>Get Out of Here: Main Action Brawn throw against an adjacent creature your size or smaller. Throw 3 squares on Weak, 5 plus Dazed 1 on Standard, 7 plus Dazed 2 on Strong; any direction, lands prone, collisions normal.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Modest for Master. Consider push 3 or letting an ally move instead; at minimum, make sure it feels distinct from Cut and Turn.</t>
+          <t>Approved: Main Action, Brawn, adjacent creature your size or smaller, free hand, 3/5/7 squares, Dazed 1/2, any direction, prone, collisions normal.</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
@@ -2668,7 +2697,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2678,17 +2707,17 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>After it finishes moving, move up to your Speed toward it without provoking. If you end adjacent, you may make one free Basic Melee attack against it using Brawn. Choose a legal route and endpoint; this does not stop or rewind its movement.</t>
+          <t>Chase up to your Speed after the enemy moves; if adjacent, make a free Basic Melee with 1 Boon and apply Slowed 1, 2 or 3 by result.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Reaction chase at full Speed plus a free attack when an enemy moves within 2. Potentially very strong and very thematic.</t>
+          <t>Reaction chase at full Speed plus a free Basic Melee with 1 Boon, then Slowed 1, 2 or 3 by result. Strong Master pursuit and a real escape punishment.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Consider once per round or a shorter chase. Playtest whether it triggers too often in open combat; the voluntary-movement clause is good.</t>
+          <t>Approved: Reaction, voluntary movement within 2, full Speed chase without provoking, free Basic Melee with 1 Boon if adjacent, Slowed 1/2/3 by result, normal decay.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -2721,15 +2750,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2843,16 +2869,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>0</v>
@@ -2876,13 +2902,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>0</v>
@@ -2996,7 +3022,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>1</v>
@@ -3005,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -3017,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
@@ -3027,7 +3053,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0</v>
@@ -3048,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
@@ -3373,15 +3399,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3405,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3420,12 +3443,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3506,30 +3528,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3553,7 +3570,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3573,7 +3589,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3593,7 +3608,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3613,7 +3627,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3633,7 +3646,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3653,7 +3665,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3673,7 +3684,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3693,7 +3703,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3713,7 +3722,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3733,7 +3741,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3753,7 +3760,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3773,23 +3779,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
